--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486964_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486964_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.5787</v>
+        <v>10.2904</v>
       </c>
       <c r="E2" t="n">
-        <v>12.3163</v>
+        <v>10.6427</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7377</v>
+        <v>-0.3523</v>
       </c>
       <c r="G2" t="n">
         <v>6.6921</v>
@@ -610,13 +610,13 @@
         <v>1.8481</v>
       </c>
       <c r="S2" t="n">
-        <v>3.0036</v>
+        <v>1.7153</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6304</v>
+        <v>0.9568</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3732</v>
+        <v>0.7585</v>
       </c>
       <c r="V2" t="n">
         <v>0.2402</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0991</v>
+        <v>3.8676</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2785</v>
+        <v>4.0766</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1794</v>
+        <v>-0.209</v>
       </c>
       <c r="G3" t="n">
         <v>2.8898</v>
@@ -688,13 +688,13 @@
         <v>1.8481</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0307</v>
+        <v>0.7991</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5851</v>
+        <v>0.213</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6158</v>
+        <v>0.5861</v>
       </c>
       <c r="V3" t="n">
         <v>0.5893</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. MILADINOVIC</t>
+          <t>F. HERNANDEZ MARTINEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7297</v>
+        <v>2.3534</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6564</v>
+        <v>1.4229</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0733</v>
+        <v>0.9305</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3686</v>
+        <v>1.302</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2869</v>
+        <v>0.305</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0817</v>
+        <v>0.997</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5542</v>
+        <v>3.077</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1729</v>
+        <v>1.5252</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3813</v>
+        <v>1.5518</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1856</v>
+        <v>-1.775</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.886</v>
+        <v>-1.2201</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2996</v>
+        <v>-0.5548</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.6962</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.3389</v>
+        <v>-2.2588</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6427</v>
+        <v>2.2588</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5377</v>
+        <v>0.462</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4411</v>
+        <v>0.0154</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0966</v>
+        <v>0.4467</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.4805</v>
+        <v>0.5893</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. HERNANDEZ MARTINEZ</t>
+          <t>G. MILADINOVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5849</v>
+        <v>0.4531</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6248</v>
+        <v>-0.3238</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9601</v>
+        <v>0.7768</v>
       </c>
       <c r="G5" t="n">
-        <v>1.302</v>
+        <v>3.3686</v>
       </c>
       <c r="H5" t="n">
-        <v>0.305</v>
+        <v>2.2869</v>
       </c>
       <c r="I5" t="n">
-        <v>0.997</v>
+        <v>1.0817</v>
       </c>
       <c r="J5" t="n">
-        <v>3.077</v>
+        <v>4.5542</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5252</v>
+        <v>3.1729</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5518</v>
+        <v>1.3813</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.775</v>
+        <v>-1.1856</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2201</v>
+        <v>-0.886</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5548</v>
+        <v>-0.2996</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>-3.6962</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2588</v>
+        <v>-5.3389</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2588</v>
+        <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3064</v>
+        <v>1.2611</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7827</v>
+        <v>0.4609</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4763</v>
+        <v>0.8002</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5893</v>
+        <v>-0.4805</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. MUKENDI MUKENDI</t>
+          <t>U. ZAMORA MAÑA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3987</v>
+        <v>0.049</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0516</v>
+        <v>-1.2366</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6529</v>
+        <v>1.2857</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6829</v>
+        <v>-1.7551</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5936</v>
+        <v>0.655</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0893</v>
+        <v>-2.4101</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-1.3457</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0939</v>
+        <v>0.5095</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.579</v>
+        <v>-1.8553</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0101</v>
+        <v>-0.4094</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4997</v>
+        <v>0.1455</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5104</v>
+        <v>-0.5548</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="R6" t="n">
-        <v>0.616</v>
+        <v>2.4641</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1905</v>
+        <v>1.1614</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2707</v>
+        <v>0.1626</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.08019999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4805</v>
+        <v>-0.5893</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6591</v>
+        <v>1.1786</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1786</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. KABASELE KASONGA</t>
+          <t>M. MUKENDI MUKENDI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.259</v>
+        <v>-0.14</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1661</v>
+        <v>1.424</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4251</v>
+        <v>-1.5639</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.6931</v>
+        <v>-1.6829</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7513</v>
+        <v>-0.5936</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9418</v>
+        <v>-1.0893</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.0647</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.1436</v>
+        <v>-0.0939</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0789</v>
+        <v>-0.579</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6284</v>
+        <v>-1.0101</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3923</v>
+        <v>-0.4997</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0208</v>
+        <v>-0.5104</v>
       </c>
       <c r="P7" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.2053</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.616</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-1.2321</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.8481</v>
-      </c>
       <c r="S7" t="n">
-        <v>2.5763</v>
+        <v>0.6518</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1307</v>
+        <v>0.6431</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4457</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2402</v>
+        <v>0.4805</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.6591</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>U. ZAMORA MAÑA</t>
+          <t>H. KABASELE KASONGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.114</v>
+        <v>-0.787</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6163</v>
+        <v>-2.2121</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7303</v>
+        <v>1.4251</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7551</v>
+        <v>-2.6931</v>
       </c>
       <c r="H8" t="n">
-        <v>0.655</v>
+        <v>-1.7513</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.4101</v>
+        <v>-0.9418</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3457</v>
+        <v>-2.0647</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5095</v>
+        <v>-2.1436</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.8553</v>
+        <v>0.0789</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4094</v>
+        <v>-0.6284</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1455</v>
+        <v>0.3923</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5548</v>
+        <v>-1.0208</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.2321</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4641</v>
+        <v>1.8481</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2264</v>
+        <v>1.5303</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2171</v>
+        <v>1.0847</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4435</v>
+        <v>0.4457</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5893</v>
+        <v>-0.2402</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7679</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CASCALES FERNANDEZ</t>
+          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2611</v>
+        <v>-1.2014</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.847</v>
+        <v>-0.6738</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4141</v>
+        <v>-0.5276</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3936</v>
+        <v>-0.8218</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3957</v>
+        <v>0.107</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7893</v>
+        <v>-0.9288</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3115</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3115</v>
+        <v>0.0779</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.6974</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.705</v>
+        <v>-0.2023</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0843</v>
+        <v>0.0291</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7893</v>
+        <v>-0.2314</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.616</v>
+        <v>1.0267</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4107</v>
+        <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2515</v>
+        <v>0.0126</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1317</v>
+        <v>-0.0543</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1197</v>
+        <v>0.0669</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
+          <t>J. CASCALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4468</v>
+        <v>-1.2314</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9488</v>
+        <v>-0.847</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.498</v>
+        <v>-0.3844</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8218</v>
+        <v>-0.3936</v>
       </c>
       <c r="H10" t="n">
-        <v>0.107</v>
+        <v>0.3957</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9288</v>
+        <v>-0.7893</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6195000000000001</v>
+        <v>0.3115</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0779</v>
+        <v>0.3115</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6974</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2023</v>
+        <v>-0.705</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0291</v>
+        <v>0.0843</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2314</v>
+        <v>-0.7893</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0267</v>
+        <v>-0.616</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0267</v>
+        <v>0.4107</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2328</v>
+        <v>-0.2218</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3294</v>
+        <v>-0.1317</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0965</v>
+        <v>-0.0901</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.666</v>
+        <v>-1.6809</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6081</v>
+        <v>-3.7713</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9422</v>
+        <v>2.0904</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5529</v>
@@ -1312,13 +1312,13 @@
         <v>1.2321</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2383</v>
+        <v>0.7468</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5928</v>
+        <v>0.244</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3546</v>
+        <v>0.5028</v>
       </c>
       <c r="V11" t="n">
         <v>1.1786</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9511</v>
+        <v>-1.9364</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0379</v>
+        <v>-3.2011</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0868</v>
+        <v>1.2647</v>
       </c>
       <c r="G12" t="n">
         <v>-2.318</v>
@@ -1390,13 +1390,13 @@
         <v>1.2321</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1526</v>
+        <v>0.862</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.527</v>
+        <v>0.3098</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3743</v>
+        <v>0.5522</v>
       </c>
       <c r="V12" t="n">
         <v>-0.4805</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.3213</v>
+        <v>-2.5891</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2727</v>
+        <v>-2.5404</v>
       </c>
       <c r="F13" t="n">
         <v>-0.0487</v>
@@ -1468,10 +1468,10 @@
         <v>1.0267</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0659</v>
+        <v>0.6663</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3952</v>
+        <v>0.337</v>
       </c>
       <c r="U13" t="n">
         <v>0.3294</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.1178</v>
+        <v>7.4473</v>
       </c>
       <c r="E14" t="n">
-        <v>2.430699999999998</v>
+        <v>2.760100000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>4.686999999999999</v>
+        <v>4.687299999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.041699999999998</v>
+        <v>-1.041699999999999</v>
       </c>
       <c r="H14" t="n">
         <v>7.088899999999999</v>
@@ -1519,10 +1519,10 @@
         <v>-8.130599999999998</v>
       </c>
       <c r="J14" t="n">
-        <v>8.028599999999997</v>
+        <v>8.028599999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>9.557599999999997</v>
+        <v>9.557599999999999</v>
       </c>
       <c r="L14" t="n">
         <v>-1.528799999999999</v>
@@ -1546,16 +1546,16 @@
         <v>17.4542</v>
       </c>
       <c r="S14" t="n">
-        <v>9.317700000000002</v>
+        <v>9.6469</v>
       </c>
       <c r="T14" t="n">
-        <v>3.911900000000001</v>
+        <v>4.2413</v>
       </c>
       <c r="U14" t="n">
-        <v>5.405999999999999</v>
+        <v>5.4059</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1314999999999999</v>
+        <v>-0.1314999999999998</v>
       </c>
       <c r="W14" t="n">
         <v>8.971</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8686</v>
+        <v>5.8285</v>
       </c>
       <c r="E15" t="n">
-        <v>5.6493</v>
+        <v>5.4401</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2192</v>
+        <v>0.3883</v>
       </c>
       <c r="G15" t="n">
         <v>2.5237</v>
@@ -1624,13 +1624,13 @@
         <v>3.6962</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5648</v>
+        <v>-1.6049</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6201</v>
+        <v>-0.8293</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9447</v>
+        <v>-0.7756</v>
       </c>
       <c r="V15" t="n">
         <v>1.4189</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4668</v>
+        <v>2.0979</v>
       </c>
       <c r="E16" t="n">
-        <v>1.239</v>
+        <v>1.5528</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2278</v>
+        <v>0.5452</v>
       </c>
       <c r="G16" t="n">
         <v>1.0095</v>
@@ -1702,13 +1702,13 @@
         <v>3.0801</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.9349</v>
+        <v>-1.3037</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2438</v>
+        <v>-0.93</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.3737</v>
       </c>
       <c r="V16" t="n">
         <v>2.5975</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. KANE</t>
+          <t>L. DIMITROVIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,22 +1735,22 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5718</v>
+        <v>0.6913</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0371</v>
+        <v>0.0984</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6089</v>
+        <v>0.5929</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4787</v>
+        <v>0.3155</v>
       </c>
       <c r="H17" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.3213</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3816</v>
+        <v>0.6368</v>
       </c>
       <c r="J17" t="n">
         <v>0.1179</v>
@@ -1762,37 +1762,37 @@
         <v>0.0789</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3609</v>
+        <v>0.1977</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0582</v>
+        <v>-0.3602</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3027</v>
+        <v>0.5579</v>
       </c>
       <c r="P17" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7632</v>
+        <v>-0.0349</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3952</v>
+        <v>-0.0194</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.368</v>
+        <v>-0.0155</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. DIMITROVIC</t>
+          <t>S. KANE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,22 +1813,22 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4682</v>
+        <v>0.5718</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0062</v>
+        <v>-0.0371</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4743</v>
+        <v>0.6089</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3155</v>
+        <v>0.4787</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3213</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6368</v>
+        <v>0.3816</v>
       </c>
       <c r="J18" t="n">
         <v>0.1179</v>
@@ -1840,37 +1840,37 @@
         <v>0.0789</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1977</v>
+        <v>0.3609</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3602</v>
+        <v>0.0582</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5579</v>
+        <v>0.3027</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.258</v>
+        <v>-0.7632</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.124</v>
+        <v>-0.3952</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.134</v>
+        <v>-0.368</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.429</v>
+        <v>-0.0054</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1293</v>
+        <v>-0.8155</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7003</v>
+        <v>0.8101</v>
       </c>
       <c r="G19" t="n">
         <v>0.4156</v>
@@ -1936,13 +1936,13 @@
         <v>1.8481</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9883</v>
+        <v>-0.5647</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7905</v>
+        <v>-0.4767</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1979</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>0.3491</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0979</v>
+        <v>-1.0682</v>
       </c>
       <c r="E20" t="n">
         <v>-0.8678</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2301</v>
+        <v>-0.2004</v>
       </c>
       <c r="G20" t="n">
         <v>0.0486</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1197</v>
+        <v>-0.0901</v>
       </c>
       <c r="T20" t="n">
         <v>0.1395</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2592</v>
+        <v>-0.2295</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. SALA VALLMAJO</t>
+          <t>I. VALERA COROMINAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1511</v>
+        <v>-1.624</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8161</v>
+        <v>-0.622</v>
       </c>
       <c r="F21" t="n">
-        <v>0.665</v>
+        <v>-1.0021</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0042</v>
+        <v>-0.0338</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3042</v>
+        <v>0.0451</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7</v>
+        <v>-0.0789</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.0601</v>
+        <v>0.1104</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.639</v>
+        <v>0.0973</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4211</v>
+        <v>0.013</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0559</v>
+        <v>-0.1441</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6653</v>
+        <v>-0.0522</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7211</v>
+        <v>-0.092</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.2053</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4107</v>
+        <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4425</v>
+        <v>-0.9928</v>
       </c>
       <c r="T21" t="n">
-        <v>0.244</v>
+        <v>-0.527</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1985</v>
+        <v>-0.4658</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. VALERA COROMINAS</t>
+          <t>P. SALA VALLMAJO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5351</v>
+        <v>-1.702</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.622</v>
+        <v>-2.1299</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9132</v>
+        <v>0.4279</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0338</v>
+        <v>-2.0042</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0451</v>
+        <v>-1.3042</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0789</v>
+        <v>-0.7</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1104</v>
+        <v>-2.0601</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0973</v>
+        <v>-0.639</v>
       </c>
       <c r="L22" t="n">
-        <v>0.013</v>
+        <v>-1.4211</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1441</v>
+        <v>0.0559</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0522</v>
+        <v>-0.6653</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.092</v>
+        <v>0.7211</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0267</v>
+        <v>0.4107</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9038</v>
+        <v>-0.1085</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.527</v>
+        <v>-0.0698</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3769</v>
+        <v>-0.0386</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3807</v>
+        <v>-3.562</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1027</v>
+        <v>-2.5211</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.278</v>
+        <v>-1.0409</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4973</v>
@@ -2248,13 +2248,13 @@
         <v>2.2588</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0353</v>
+        <v>-1.2166</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7518</v>
+        <v>-1.1702</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2835</v>
+        <v>-0.0464</v>
       </c>
       <c r="V23" t="n">
         <v>1.1786</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9061</v>
+        <v>-3.7632</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4829</v>
+        <v>-3.0645</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4232</v>
+        <v>-0.6988</v>
       </c>
       <c r="G24" t="n">
         <v>-3.6943</v>
@@ -2326,13 +2326,13 @@
         <v>3.0801</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0126</v>
+        <v>-0.8698</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2438</v>
+        <v>-0.8254</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2312</v>
+        <v>-0.0443</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0472</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9932</v>
+        <v>-3.8851</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.5114</v>
+        <v>-1.7206</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4818</v>
+        <v>-2.1645</v>
       </c>
       <c r="G25" t="n">
         <v>4.4798</v>
@@ -2404,13 +2404,13 @@
         <v>2.0534</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1794</v>
+        <v>-1.0712</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0931</v>
+        <v>-0.3023</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0862</v>
+        <v>-0.7689</v>
       </c>
       <c r="V25" t="n">
         <v>-3.1868</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.117700000000001</v>
+        <v>-6.420399999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.687200000000001</v>
+        <v>-4.687199999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.4308</v>
+        <v>-1.7334</v>
       </c>
       <c r="G26" t="n">
         <v>1.0418</v>
@@ -2482,13 +2482,13 @@
         <v>18.4808</v>
       </c>
       <c r="S26" t="n">
-        <v>-9.317499999999999</v>
+        <v>-8.620399999999998</v>
       </c>
       <c r="T26" t="n">
         <v>-5.4058</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.9117</v>
+        <v>-3.214299999999999</v>
       </c>
       <c r="V26" t="n">
         <v>0.1314000000000002</v>
